--- a/results/naturverbundenheit/explaining_features/nature-dataset-pairwise_explainable_distances-jensenshannon-auto.xlsx
+++ b/results/naturverbundenheit/explaining_features/nature-dataset-pairwise_explainable_distances-jensenshannon-auto.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH34"/>
+  <dimension ref="A1:AJ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,130 +471,140 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>France</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Peru</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>United Arab Emirates</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>United States of America</t>
         </is>
@@ -610,100 +620,106 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000822133558341067</v>
+        <v>0.0007547727644637577</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004975931583230413</v>
+        <v>0.000455936359302488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001795511582342948</v>
+        <v>0.001643022707642406</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0006746521545714863</v>
+        <v>0.0006201021493189699</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007703271901292269</v>
+        <v>0.0007047953312153674</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000840443038785935</v>
+        <v>0.0007738998325191075</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002993898715157413</v>
+        <v>0.0006801051364276834</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002370977348174035</v>
+        <v>0.0002767035562537558</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004412217753125981</v>
+        <v>0.0003273577902033063</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006905394368310204</v>
+        <v>0.002182785790608733</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008337834934306136</v>
+        <v>0.0004077542070976025</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0005498013765232767</v>
+        <v>0.0006382512361971633</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001110434861344296</v>
+        <v>0.0007678861200327546</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002101692376096767</v>
+        <v>0.0005075967634391178</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002059482053202338</v>
+        <v>0.001026537600813958</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008189922729503124</v>
+        <v>0.00192771002194531</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008887133956466591</v>
+        <v>0.001895939377903669</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007050846297166995</v>
+        <v>0.0007513823518797356</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0005760128114861237</v>
+        <v>0.0008167300906715516</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0003793657246042414</v>
+        <v>0.0006526162870328111</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001285523830074373</v>
+        <v>0.0005304475332657358</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001242476340006791</v>
+        <v>0.0003493494258047794</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0006717050346133899</v>
+        <v>0.001179816452803758</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0006704553353592415</v>
+        <v>0.001142666634345456</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0008985992099697465</v>
+        <v>0.0006170372965547407</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00085192071921391</v>
+        <v>0.0006143655114641051</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0003568289358862321</v>
+        <v>0.0008260085888793886</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0007105978158151942</v>
+        <v>0.0007807645613429068</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0007563564359911485</v>
+        <v>0.000329360095738865</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0007968616093256464</v>
+        <v>0.0006556667698393208</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0003622270266783732</v>
+        <v>0.0006960329494242858</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0004395683556382205</v>
+        <v>0.0007327539440427072</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.0003332940231162733</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.0004026950764687538</v>
       </c>
     </row>
     <row r="3">
@@ -713,103 +729,109 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000822133558341067</v>
+        <v>0.0007547727644637577</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004922410611134709</v>
+        <v>0.0004521976151283271</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001696304262163331</v>
+        <v>0.001556911598655077</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002220871430658897</v>
+        <v>0.0002031194462676088</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003131196769296613</v>
+        <v>0.0002857227221755371</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0003950777432340214</v>
+        <v>0.0003614820689809065</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007664291659411899</v>
+        <v>0.0002646621388591174</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002119430929445456</v>
+        <v>0.0007027388915310703</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00142331333018145</v>
+        <v>0.0006443074584749673</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004660601886133021</v>
+        <v>0.001951346107667273</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001237766878734239</v>
+        <v>0.001312985823822321</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004459208636604501</v>
+        <v>0.0004302676531000359</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001168828788397154</v>
+        <v>0.001143739819772061</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001865729490015691</v>
+        <v>0.0004090405379661474</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00201276022036594</v>
+        <v>0.001079552523410379</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003557258941439807</v>
+        <v>0.001714193037183107</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002410175133161878</v>
+        <v>0.001852020160775047</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006583414051797176</v>
+        <v>0.0003240206069202329</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0006305282595228209</v>
+        <v>0.0002189391137765073</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0006901420299640717</v>
+        <v>0.0006037106933193898</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003756265918056387</v>
+        <v>0.0005779844789275251</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001726758319571866</v>
+        <v>0.0006324258913863967</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008236302145363631</v>
+        <v>0.0003474782585731413</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0006349636716968976</v>
+        <v>0.00158854422249802</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001158520461449765</v>
+        <v>0.0007585036410811811</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0004412952736959169</v>
+        <v>0.000580942470890185</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0006726489226879656</v>
+        <v>0.001065139016481779</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0005277097173825658</v>
+        <v>0.0004015776054006642</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0005443910560980392</v>
+        <v>0.0006130862589778318</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001099873854784032</v>
+        <v>0.000482713742164949</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.00110236063116846</v>
+        <v>0.0004987539268456534</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0008212487233807039</v>
+        <v>0.001006208961679693</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.001015511830969264</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.0007543415635248042</v>
       </c>
     </row>
     <row r="4">
@@ -819,103 +841,109 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0004975931583230413</v>
+        <v>0.000455936359302488</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004922410611134709</v>
+        <v>0.0004521976151283271</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002002804171927259</v>
+        <v>0.001836203420520819</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006328714808025685</v>
+        <v>0.0005800273528261023</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005664885399453699</v>
+        <v>0.0005161767068399693</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009364326218681571</v>
+        <v>0.0008612002540587891</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005180126537344264</v>
+        <v>0.0004144410229237742</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002745430312570227</v>
+        <v>0.0004741837258138958</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008348789454334733</v>
+        <v>0.000437535456179737</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00036842826269495</v>
+        <v>0.002527319167417424</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001203277379603943</v>
+        <v>0.0007713868195552951</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0008033945522718587</v>
+        <v>0.000336789565809977</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001459206940921373</v>
+        <v>0.001107248173007076</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002807867672898739</v>
+        <v>0.0007394946752246386</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002365799067373487</v>
+        <v>0.001348079797551557</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0005338958275672582</v>
+        <v>0.00257823239351562</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0005510999105076578</v>
+        <v>0.002181776746351369</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008475453567342726</v>
+        <v>0.000487818100482459</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007014179274033943</v>
+        <v>0.0005042383120965963</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0004163623335423063</v>
+        <v>0.0007818401563334951</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0007311358003321603</v>
+        <v>0.0006436570124060748</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002204984849524605</v>
+        <v>0.0003803148291132192</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002443025485144512</v>
+        <v>0.000670622510061144</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.000628000880164708</v>
+        <v>0.002032329871801095</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001651639777173672</v>
+        <v>0.0002255672424890834</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.000463096989072066</v>
+        <v>0.0005744231637729196</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0005465416871457381</v>
+        <v>0.0015189479695366</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0002714398906704753</v>
+        <v>0.0004239593281928185</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0008111648882581048</v>
+        <v>0.0004994610340200813</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0009387980959422803</v>
+        <v>0.0002506604538193051</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0008361026982451372</v>
+        <v>0.0007436574021558543</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0005896801730930205</v>
+        <v>0.0008647056985674345</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.0007688982114794731</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.000540203006459825</v>
       </c>
     </row>
     <row r="5">
@@ -925,103 +953,109 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001795511582342948</v>
+        <v>0.001643022707642406</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001696304262163331</v>
+        <v>0.001556911598655077</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002002804171927259</v>
+        <v>0.001836203420520819</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00142899341273105</v>
+        <v>0.001309905814605516</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001602269529566946</v>
+        <v>0.001466943614448067</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001341884652408871</v>
+        <v>0.001228932962341843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001613051184956442</v>
+        <v>0.001437056089075383</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009590577554713072</v>
+        <v>0.001485361872472369</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001924717489605167</v>
+        <v>0.001424630098534901</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001882339665931104</v>
+        <v>0.0008888955432079883</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001234524532607712</v>
+        <v>0.001771832031810945</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001117994958976783</v>
+        <v>0.001735572860298947</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001079655107282884</v>
+        <v>0.001136861929712714</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001502246471659168</v>
+        <v>0.001025389845747105</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001246934388304029</v>
+        <v>0.0009957327610037954</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001741653490483075</v>
+        <v>0.001381184326616107</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001568879020927439</v>
+        <v>0.00114987656579224</v>
       </c>
       <c r="T5" t="n">
-        <v>0.001092728743153681</v>
+        <v>0.001597857843204874</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001212022234702346</v>
+        <v>0.001437405552603658</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001715735845593226</v>
+        <v>0.0009992155358962711</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002166086743185375</v>
+        <v>0.001111636645602888</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001737144491899774</v>
+        <v>0.001576421819715787</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002009330438616594</v>
+        <v>0.001985685210586573</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001555082757405248</v>
+        <v>0.001599456862301244</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001114406322397396</v>
+        <v>0.001847570421228349</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001722768245534182</v>
+        <v>0.00143271442785617</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.001562866630468713</v>
+        <v>0.00102360243704858</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.002256965051599172</v>
+        <v>0.001578350918414937</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001167786952271799</v>
+        <v>0.001439243799055461</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00192418819958491</v>
+        <v>0.002072917883536743</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001664856750988457</v>
+        <v>0.001075356221479535</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.001203540233413925</v>
+        <v>0.00176641522965629</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.001529812442630157</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.001105107074934204</v>
       </c>
     </row>
     <row r="6">
@@ -1031,103 +1065,109 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0006746521545714863</v>
+        <v>0.0006201021493189699</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002220871430658897</v>
+        <v>0.0002031194462676088</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0006328714808025685</v>
+        <v>0.0005800273528261023</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00142899341273105</v>
+        <v>0.001309905814605516</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000114967379110448</v>
+        <v>0.000106663510096261</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001090849754828014</v>
+        <v>0.000102045259604506</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004947884046068711</v>
+        <v>0.0001144453098091382</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001614962489796278</v>
+        <v>0.0004549824460778262</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00101120200675879</v>
+        <v>0.000413181601293924</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000415235930512198</v>
+        <v>0.001487292959890949</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0007619061382675236</v>
+        <v>0.0009332602920010579</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001660008710754395</v>
+        <v>0.0003868179966660781</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006464911655203247</v>
+        <v>0.0007033105235653323</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001265994313278134</v>
+        <v>0.0001538754566632367</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001434451544444763</v>
+        <v>0.0005991553224515</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001725593825517382</v>
+        <v>0.00116065673656987</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001245285118110584</v>
+        <v>0.001320009058069339</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0003414934695383849</v>
+        <v>0.0001578723007141525</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0003174680774846106</v>
+        <v>0.00011489465301223</v>
       </c>
       <c r="V6" t="n">
-        <v>0.000455073023747102</v>
+        <v>0.0003132172663195925</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001002799183320044</v>
+        <v>0.0002912171781505407</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001265633645241133</v>
+        <v>0.0004182263867419105</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0006633132084911676</v>
+        <v>0.0009201272834805371</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0003495230634467284</v>
+        <v>0.001163475688143723</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0007002475755859105</v>
+        <v>0.0006116162362548135</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0002918294706358513</v>
+        <v>0.0003208146939314943</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0004132250741621741</v>
+        <v>0.0006436485933496159</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0004842410899607567</v>
+        <v>0.0002661216037368953</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0002503286509666548</v>
+        <v>0.0003771330630226638</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0009294636274873341</v>
+        <v>0.0004447822162491587</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0007376367844341717</v>
+        <v>0.0002300155109826756</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0008691377581414224</v>
+        <v>0.0008517331751441541</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0006808024429510304</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.0007971401356311099</v>
       </c>
     </row>
     <row r="7">
@@ -1137,103 +1177,109 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007703271901292269</v>
+        <v>0.0007047953312153674</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003131196769296613</v>
+        <v>0.0002857227221755371</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0005664885399453699</v>
+        <v>0.0005161767068399693</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001602269529566946</v>
+        <v>0.001466943614448067</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000114967379110448</v>
+        <v>0.000106663510096261</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001566892482517563</v>
+        <v>0.000144711240655027</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003524335801146948</v>
+        <v>7.127937911879793e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001866055064918598</v>
+        <v>0.0003210310281669928</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009263050004720333</v>
+        <v>0.0002631292030232849</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001804684507307659</v>
+        <v>0.001718257253382284</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0008981712580949055</v>
+        <v>0.0008532960026953237</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0002674481928356883</v>
+        <v>0.0001656602717677281</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008604183554269321</v>
+        <v>0.0008272493823242662</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001721778989167652</v>
+        <v>0.0002463098215818604</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001748684424425523</v>
+        <v>0.0007971498835169363</v>
       </c>
       <c r="R7" t="n">
-        <v>3.640618836937009e-05</v>
+        <v>0.0015794791170509</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000181711983251215</v>
+        <v>0.001607883038063238</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003746841703850956</v>
+        <v>3.343369806041893e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002566572101739334</v>
+        <v>0.0001661572102916005</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002618473708514384</v>
+        <v>0.0003436155027757735</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001222307910914956</v>
+        <v>0.0002349793762658426</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001847527357016201</v>
+        <v>0.0002385415076228028</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.000600682608072051</v>
+        <v>0.001123201239531696</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001894688456317687</v>
+        <v>0.001700395903832415</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001010933927398733</v>
+        <v>0.0005518773139429644</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.58077909639838e-05</v>
+        <v>0.0001747942434498551</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0002621131614792093</v>
+        <v>0.0009289500676977891</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0002614458646951273</v>
+        <v>7.736677851482131e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0001992397482210417</v>
+        <v>0.0002358237791211742</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.00114722149780883</v>
+        <v>0.0002380224136395489</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0006679623851152981</v>
+        <v>0.0001824717348529485</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0008031273095609697</v>
+        <v>0.001049355072041059</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0006143365160705871</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.0007295634316116848</v>
       </c>
     </row>
     <row r="8">
@@ -1243,2858 +1289,3244 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000840443038785935</v>
+        <v>0.0007738998325191075</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003950777432340214</v>
+        <v>0.0003614820689809065</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009364326218681571</v>
+        <v>0.0008612002540587891</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001341884652408871</v>
+        <v>0.001228932962341843</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001090849754828014</v>
+        <v>0.000102045259604506</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001566892482517563</v>
+        <v>0.000144711240655027</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000492269866435577</v>
+        <v>0.0002344073996684964</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001452618110139279</v>
+        <v>0.0004521571764445268</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009656339868743072</v>
+        <v>0.0003975054542769735</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005946475639247767</v>
+        <v>0.001336532049987678</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0006190050994747668</v>
+        <v>0.0008905801879682648</v>
       </c>
       <c r="N8" t="n">
-        <v>8.633540494025963e-05</v>
+        <v>0.0005511723638339649</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0004422859433837749</v>
+        <v>0.0005736508260438863</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00111959938163088</v>
+        <v>7.961787049186009e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001248239491297517</v>
+        <v>0.0004113136866818844</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0002445006099946157</v>
+        <v>0.001025081438133275</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003014856284530918</v>
+        <v>0.001147679963970996</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0002239784832647796</v>
+        <v>0.0002254224393480486</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0002234473306927694</v>
+        <v>0.0002787992941303312</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004864994635254567</v>
+        <v>0.000204720468939069</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00133330946446869</v>
+        <v>0.0002037748402321331</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001273000945488025</v>
+        <v>0.0004471439480205934</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0008579746721776212</v>
+        <v>0.001226397297857511</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0003079788323795797</v>
+        <v>0.001171044663320596</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.000498931608183618</v>
+        <v>0.0007949968382678804</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.000426092386869266</v>
+        <v>0.0002824373298970249</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.000387204691291828</v>
+        <v>0.0004586960877391048</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0007198097580423382</v>
+        <v>0.0003887959328761918</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0001801426202293689</v>
+        <v>0.0003524924095475407</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001065105008963174</v>
+        <v>0.000661694094570018</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0006370883985794981</v>
+        <v>0.0001641081745500216</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0009688868282246409</v>
+        <v>0.0009771779376524848</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.0005875707326249558</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.0008871872360489022</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0002993898715157413</v>
+        <v>0.0006801051364276834</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0007664291659411899</v>
+        <v>0.0002646621388591174</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0005180126537344264</v>
+        <v>0.0004144410229237742</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001613051184956442</v>
+        <v>0.001437056089075383</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0004947884046068711</v>
+        <v>0.0001144453098091382</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003524335801146948</v>
+        <v>7.127937911879793e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000492269866435577</v>
+        <v>0.0002344073996684964</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002072851151049829</v>
+        <v>0.0004107481668841814</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000226977420568175</v>
+        <v>0.0003481934900644648</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003685083789556087</v>
+        <v>0.001671314212811978</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0006347642436805731</v>
+        <v>0.0009410042218419653</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0003401561721076939</v>
+        <v>0.0001882529004701282</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0008158169404592388</v>
+        <v>0.0007800270132522611</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001976101023077506</v>
+        <v>0.0002905305227297225</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001824033305561015</v>
+        <v>0.0008379816436318398</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0003768135811888518</v>
+        <v>0.001602523624396663</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0007433157877822931</v>
+        <v>0.00147100023656706</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0004315520136920724</v>
+        <v>8.30349071068523e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0002139899401579091</v>
+        <v>8.413113393437093e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>4.395259697987325e-05</v>
+        <v>0.0003545424126014538</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001584249512156351</v>
+        <v>0.0002626741091581477</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001753817768437563</v>
+        <v>0.0003209179336690769</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0005933479887679188</v>
+        <v>0.0009870790919205808</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0002089090324581867</v>
+        <v>0.001655830099713792</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0008628443351934343</v>
+        <v>0.0004422534211602636</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0004231762476388277</v>
+        <v>0.0002084422843551238</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.436828701998398e-05</v>
+        <v>0.0009968543668672106</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0004208804738280851</v>
+        <v>0.0001100786368624052</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0003501762099204773</v>
+        <v>0.000351065904478879</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001178319022825877</v>
+        <v>0.0002184717153921187</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0001022423530875212</v>
+        <v>0.0002233319533999849</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0003989846598532089</v>
+        <v>0.00086179610112322</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0007133931599123397</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.0007381343346261206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002370977348174035</v>
+        <v>0.0002767035562537558</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002119430929445456</v>
+        <v>0.0007027388915310703</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002745430312570227</v>
+        <v>0.0004741837258138958</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0009590577554713072</v>
+        <v>0.001485361872472369</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001614962489796278</v>
+        <v>0.0004549824460778262</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001866055064918598</v>
+        <v>0.0003210310281669928</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001452618110139279</v>
+        <v>0.0004521571764445268</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002072851151049829</v>
+        <v>0.0004107481668841814</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002384426772718246</v>
+        <v>1.822660022440119e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002496872119180981</v>
+        <v>0.001913304967070645</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001054171252268063</v>
+        <v>0.0002105356316025409</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001275012880373778</v>
+        <v>0.00034023512576181</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0008073175531097315</v>
+        <v>0.000584932086970808</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0004361028427115989</v>
+        <v>0.0003156867550425269</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0002950329380669018</v>
+        <v>0.0007580187178026607</v>
       </c>
       <c r="R10" t="n">
-        <v>0.002042949739237347</v>
+        <v>0.001812581555911887</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001682187356177555</v>
+        <v>0.001680716548413017</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001070533652689224</v>
+        <v>0.0003460825340976554</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001313833219614965</v>
+        <v>0.0006830375806820331</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002151444118866521</v>
+        <v>0.0003994586326522873</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002771334381978324</v>
+        <v>0.0001979728921762366</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001359737251827888</v>
+        <v>4.075639777228379e-05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.002644161984750589</v>
+        <v>0.001457688761406919</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001736381397792583</v>
+        <v>0.001618374181006107</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0009156049330775972</v>
+        <v>0.0005470950073030169</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.002046437451690213</v>
+        <v>0.0001913411960153858</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.00198421236456719</v>
+        <v>0.0007963779503813845</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.002908325501853875</v>
+        <v>0.0003879237067488796</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.001099690467847303</v>
+        <v>1.357558324999227e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.002069556331216138</v>
+        <v>0.0003868418662462296</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002109692351047512</v>
+        <v>0.0003223407711684459</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.002097903732869841</v>
+        <v>0.001085342051296152</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>9.479217474500328e-05</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.0003660899335937388</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0004412217753125981</v>
+        <v>0.0003273577902033063</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00142331333018145</v>
+        <v>0.0006443074584749673</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0008348789454334733</v>
+        <v>0.000437535456179737</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001924717489605167</v>
+        <v>0.001424630098534901</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00101120200675879</v>
+        <v>0.000413181601293924</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0009263050004720333</v>
+        <v>0.0002631292030232849</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0009656339868743072</v>
+        <v>0.0003975054542769735</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000226977420568175</v>
+        <v>0.0003481934900644648</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002384426772718246</v>
+        <v>1.822660022440119e-05</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001026905738448444</v>
+        <v>0.001861403380999683</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0005416955922223094</v>
+        <v>0.0002247664641372058</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0007324841287714046</v>
+        <v>0.0003144189296914091</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0008771448962122055</v>
+        <v>0.0005454936265547468</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002167848650811117</v>
+        <v>0.0002989463703367437</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001875928671390828</v>
+        <v>0.0007275007767709907</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0009609441006345953</v>
+        <v>0.001783541595452797</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001379380819484409</v>
+        <v>0.001612373706804183</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0006960949910276221</v>
+        <v>0.0002911677171059705</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0004806290282039246</v>
+        <v>0.0006041362066019937</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0002956962265744468</v>
+        <v>0.0003419542614266625</v>
       </c>
       <c r="W11" t="n">
-        <v>0.002085126470484242</v>
+        <v>0.0001390801464763738</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001654935607047108</v>
+        <v>2.774242433243853e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.000819951659766891</v>
+        <v>0.001365694734191177</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0005151443594724576</v>
+        <v>0.00158854639330044</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0009767973534421314</v>
+        <v>0.0004844895319552453</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001018486140962187</v>
+        <v>0.0001154691307259772</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0003022135642022283</v>
+        <v>0.0008024508147327597</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0009420012257357977</v>
+        <v>0.0003134854059379621</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0007448324758642853</v>
+        <v>1.980039061834554e-05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.00130429696828827</v>
+        <v>0.0003383802329893899</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0001307230406540463</v>
+        <v>0.0002573467933595503</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0008302898942415286</v>
+        <v>0.0009824199886030677</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.0001192768454337162</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.000431789655251773</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0006905394368310204</v>
+        <v>0.002182785790608733</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0004660601886133021</v>
+        <v>0.001951346107667273</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00036842826269495</v>
+        <v>0.002527319167417424</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001882339665931104</v>
+        <v>0.0008888955432079883</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000415235930512198</v>
+        <v>0.001487292959890949</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001804684507307659</v>
+        <v>0.001718257253382284</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0005946475639247767</v>
+        <v>0.001336532049987678</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0003685083789556087</v>
+        <v>0.001671314212811978</v>
       </c>
       <c r="J12" t="n">
-        <v>0.002496872119180981</v>
+        <v>0.001913304967070645</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001026905738448444</v>
+        <v>0.001861403380999683</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.001395494939835793</v>
+        <v>0.002200230829354894</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0006249383115406926</v>
+        <v>0.002312146471779976</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001500705860874506</v>
+        <v>0.0009704691802525455</v>
       </c>
       <c r="P12" t="n">
-        <v>0.002575642005465444</v>
+        <v>0.001175353050222266</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.002458556490846172</v>
+        <v>0.0007403588000231334</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0001825771650526635</v>
+        <v>0.0003980647080438026</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0003700053498817857</v>
+        <v>0.0002666862601894223</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0007720724372047881</v>
+        <v>0.001883453115160795</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0005419190584215884</v>
+        <v>0.001553513234853845</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0002693902948423307</v>
+        <v>0.0009790949008548497</v>
       </c>
       <c r="W12" t="n">
-        <v>0.001269103831162302</v>
+        <v>0.001210844948078662</v>
       </c>
       <c r="X12" t="n">
-        <v>0.00248304301091952</v>
+        <v>0.001984402940698347</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0005167023291746335</v>
+        <v>0.002551935220806439</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0003960969089634869</v>
+        <v>0.001253215704542814</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.001636244959534286</v>
+        <v>0.00243760390415735</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.733048680003559e-05</v>
+        <v>0.001604375138620095</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0003240969929131481</v>
+        <v>0.0008450477278618562</v>
       </c>
       <c r="AD12" t="n">
-        <v>9.254133801157968e-05</v>
+        <v>0.001882779321381557</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0005282140872573138</v>
+        <v>0.001832932530149019</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.001298151159541111</v>
+        <v>0.002679778215137817</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0007985210307114768</v>
+        <v>0.001018702756597264</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0005873371268735817</v>
+        <v>0.001903179696257075</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.001944814843562906</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.00193483644979774</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0008337834934306136</v>
+        <v>0.0004077542070976025</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001237766878734239</v>
+        <v>0.001312985823822321</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001203277379603943</v>
+        <v>0.0007713868195552951</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001234524532607712</v>
+        <v>0.001771832031810945</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0007619061382675236</v>
+        <v>0.0009332602920010579</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0008981712580949055</v>
+        <v>0.0008532960026953237</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0006190050994747668</v>
+        <v>0.0008905801879682648</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0006347642436805731</v>
+        <v>0.0009410042218419653</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001054171252268063</v>
+        <v>0.0002105356316025409</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0005416955922223094</v>
+        <v>0.0002247664641372058</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001395494939835793</v>
+        <v>0.002200230829354894</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0004146556098239646</v>
+        <v>0.0009497535976686906</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0001954978713326299</v>
+        <v>0.0004988085668398622</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001010422403870496</v>
+        <v>0.0006791778429818532</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0006208680889591209</v>
+        <v>0.0008141828334986893</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0009661718559023261</v>
+        <v>0.001991225820532009</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001021639259119062</v>
+        <v>0.001733775924531592</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0002055373749003327</v>
+        <v>0.0008870590821738612</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0002787667014334193</v>
+        <v>0.001273442828602049</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0006779095717961542</v>
+        <v>0.0006456298934670515</v>
       </c>
       <c r="W13" t="n">
-        <v>0.001881022946944572</v>
+        <v>0.0004457755508827178</v>
       </c>
       <c r="X13" t="n">
-        <v>0.001005104152889755</v>
+        <v>0.0002736885649748583</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.001131428988374953</v>
+        <v>0.001923519465921098</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0005033470694677621</v>
+        <v>0.001527867656962752</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0003215885878310229</v>
+        <v>0.000758091903814427</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.001159856778267721</v>
+        <v>0.0004746655302521723</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0006355516513227594</v>
+        <v>0.0009028975291566211</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.001408366759400697</v>
+        <v>0.0009386981595419807</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0003813039578177212</v>
+        <v>0.0002817492987649042</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001112212321176857</v>
+        <v>0.0008723806560342092</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0005233106718387654</v>
+        <v>0.0006870397710954473</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001103597094871415</v>
+        <v>0.001204212545005291</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.0001211958553906719</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.0007653477736133719</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0005498013765232767</v>
+        <v>0.0006382512361971633</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0004459208636604501</v>
+        <v>0.0004302676531000359</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0008033945522718587</v>
+        <v>0.000336789565809977</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001117994958976783</v>
+        <v>0.001735572860298947</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0001660008710754395</v>
+        <v>0.0003868179966660781</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002674481928356883</v>
+        <v>0.0001656602717677281</v>
       </c>
       <c r="H14" t="n">
-        <v>8.633540494025963e-05</v>
+        <v>0.0005511723638339649</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0003401561721076939</v>
+        <v>0.0001882529004701282</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001275012880373778</v>
+        <v>0.00034023512576181</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0007324841287714046</v>
+        <v>0.0003144189296914091</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0006249383115406926</v>
+        <v>0.002312146471779976</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0004146556098239646</v>
+        <v>0.0009497535976686906</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0002977297288853065</v>
+        <v>0.001289199270304882</v>
       </c>
       <c r="P14" t="n">
-        <v>0.001061765257266248</v>
+        <v>0.000582241558013218</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.001053061726998762</v>
+        <v>0.00139644282909571</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0003511518014231094</v>
+        <v>0.002373404096783979</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0003935304423977201</v>
+        <v>0.002270122544694154</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0001297300971004234</v>
+        <v>0.0001691825019037364</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001417570212613574</v>
+        <v>0.0003414984401896217</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0004041447949919583</v>
+        <v>0.0007160288281777605</v>
       </c>
       <c r="W14" t="n">
-        <v>0.001270951377707928</v>
+        <v>0.0005012232283111047</v>
       </c>
       <c r="X14" t="n">
-        <v>0.001073571061846904</v>
+        <v>0.0002485383334990317</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0007715306325478924</v>
+        <v>0.001169889946327615</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0003069984941326503</v>
+        <v>0.002294766277059003</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0002863494369617702</v>
+        <v>0.00047486127750388</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0005292452486440013</v>
+        <v>0.0003660255095482305</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0002781741912163569</v>
+        <v>0.00151326028929544</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0007753213606968911</v>
+        <v>8.184360849392175e-05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0001597753122251881</v>
+        <v>0.0002974829067311284</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0009369026776663298</v>
+        <v>8.269582661849213e-05</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.000414290060890749</v>
+        <v>0.0004895935199840354</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0006283804084501329</v>
+        <v>0.001193228641182339</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.0007378371313146545</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.0005413141829479201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.001110434861344296</v>
+        <v>0.0007678861200327546</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001168828788397154</v>
+        <v>0.001143739819772061</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001459206940921373</v>
+        <v>0.001107248173007076</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001079655107282884</v>
+        <v>0.001136861929712714</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0006464911655203247</v>
+        <v>0.0007033105235653323</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0008604183554269321</v>
+        <v>0.0008272493823242662</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0004422859433837749</v>
+        <v>0.0005736508260438863</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0008158169404592388</v>
+        <v>0.0007800270132522611</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0008073175531097315</v>
+        <v>0.000584932086970808</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0008771448962122055</v>
+        <v>0.0005454936265547468</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001500705860874506</v>
+        <v>0.0009704691802525455</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0001954978713326299</v>
+        <v>0.0004988085668398622</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0002977297288853065</v>
+        <v>0.001289199270304882</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0006551576834604447</v>
+        <v>0.0003857763093284138</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0004332937279756033</v>
+        <v>0.0001827310366358925</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0009853846655032564</v>
+        <v>0.0009289847001239207</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0009427400927546259</v>
+        <v>0.0005718779547835796</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0002357750824579874</v>
+        <v>0.0008886757856863931</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0003892960266013671</v>
+        <v>0.0009446330973876842</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0009078877578437231</v>
+        <v>0.0001891023600577335</v>
       </c>
       <c r="W15" t="n">
-        <v>0.001964024177424147</v>
+        <v>0.0002566338968353837</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0008709530946671485</v>
+        <v>0.0006234331826337323</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.001226816991512277</v>
+        <v>0.001738751139820351</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0007078920559901747</v>
+        <v>0.0009302886180025908</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0001605406551612901</v>
+        <v>0.001043562066994184</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.001199446411302169</v>
+        <v>0.0004614748764536193</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0007681800900361795</v>
+        <v>0.0003026639935682863</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.001637738924700102</v>
+        <v>0.00106316065206885</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0004198899322241442</v>
+        <v>0.0005875446479687256</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.001211217256989852</v>
+        <v>0.001298225664156673</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0007199416592024963</v>
+        <v>0.0003513827322599993</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.001256690773665351</v>
+        <v>0.001023997836150762</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.0004820587851153488</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.001017213217113181</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.002101692376096767</v>
+        <v>0.0005075967634391178</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001865729490015691</v>
+        <v>0.0004090405379661474</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002807867672898739</v>
+        <v>0.0007394946752246386</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001502246471659168</v>
+        <v>0.001025389845747105</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001265994313278134</v>
+        <v>0.0001538754566632367</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001721778989167652</v>
+        <v>0.0002463098215818604</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00111959938163088</v>
+        <v>7.961787049186009e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001976101023077506</v>
+        <v>0.0002905305227297225</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0004361028427115989</v>
+        <v>0.0003156867550425269</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002167848650811117</v>
+        <v>0.0002989463703367437</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002575642005465444</v>
+        <v>0.001175353050222266</v>
       </c>
       <c r="M16" t="n">
-        <v>0.001010422403870496</v>
+        <v>0.0006791778429818532</v>
       </c>
       <c r="N16" t="n">
-        <v>0.001061765257266248</v>
+        <v>0.000582241558013218</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0006551576834604447</v>
+        <v>0.0003857763093284138</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0004506220249098036</v>
+        <v>0.0002769334257753049</v>
       </c>
       <c r="R16" t="n">
-        <v>0.001905890187433378</v>
+        <v>0.0009731681211837644</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001575541937995674</v>
+        <v>0.0009669520684153514</v>
       </c>
       <c r="T16" t="n">
-        <v>0.001129207530400029</v>
+        <v>0.0003245497487817344</v>
       </c>
       <c r="U16" t="n">
-        <v>0.001314962495435293</v>
+        <v>0.000362852735203119</v>
       </c>
       <c r="V16" t="n">
-        <v>0.002125240561508393</v>
+        <v>0.0001192418204722788</v>
       </c>
       <c r="W16" t="n">
-        <v>0.002623478221648843</v>
+        <v>0.0001302319231303741</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0006384112596619089</v>
+        <v>0.0003752493570915656</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.002627488709339958</v>
+        <v>0.001169921300370555</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.001696145906873619</v>
+        <v>0.0009872349880386405</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.000579821799164318</v>
+        <v>0.0007135202835157633</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.002106672589418343</v>
+        <v>0.0002834291781065498</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.001891856234045607</v>
+        <v>0.000262672720055964</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.002832744327091317</v>
+        <v>0.0004855538673447159</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.001152953884313398</v>
+        <v>0.0002570700728000484</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.001800708939275026</v>
+        <v>0.0007159141578456929</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.001852270625718384</v>
+        <v>0.0001481198400478676</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.002436956164627873</v>
+        <v>0.0008589785769892768</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.0003839532349318538</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.0005777622690089026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.002059482053202338</v>
+        <v>0.001026537600813958</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00201276022036594</v>
+        <v>0.001079552523410379</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002365799067373487</v>
+        <v>0.001348079797551557</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001246934388304029</v>
+        <v>0.0009957327610037954</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001434451544444763</v>
+        <v>0.0005991553224515</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001748684424425523</v>
+        <v>0.0007971498835169363</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001248239491297517</v>
+        <v>0.0004113136866818844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.001824033305561015</v>
+        <v>0.0008379816436318398</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0002950329380669018</v>
+        <v>0.0007580187178026607</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001875928671390828</v>
+        <v>0.0007275007767709907</v>
       </c>
       <c r="L17" t="n">
-        <v>0.002458556490846172</v>
+        <v>0.0007403588000231334</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0006208680889591209</v>
+        <v>0.0008141828334986893</v>
       </c>
       <c r="N17" t="n">
-        <v>0.001053061726998762</v>
+        <v>0.00139644282909571</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0004332937279756033</v>
+        <v>0.0001827310366358925</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0004506220249098036</v>
+        <v>0.0002769334257753049</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.001892489048909762</v>
+        <v>0.000598321697506981</v>
       </c>
       <c r="S17" t="n">
-        <v>0.001502093288561322</v>
+        <v>0.0003967740579882089</v>
       </c>
       <c r="T17" t="n">
-        <v>0.000834055744066191</v>
+        <v>0.0009120163896364781</v>
       </c>
       <c r="U17" t="n">
-        <v>0.00105625758944865</v>
+        <v>0.0008728871122113558</v>
       </c>
       <c r="V17" t="n">
-        <v>0.001919130442407346</v>
+        <v>0.0002170498380736429</v>
       </c>
       <c r="W17" t="n">
-        <v>0.002625988961381088</v>
+        <v>0.0003611400526751314</v>
       </c>
       <c r="X17" t="n">
-        <v>0.001002240573863264</v>
+        <v>0.0008426761466731178</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.001998407576051388</v>
+        <v>0.001810731174035727</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.001468260481752453</v>
+        <v>0.0008004786135067206</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.000684883988367931</v>
+        <v>0.001137226250333115</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.001978411582784225</v>
+        <v>0.0006551269598988984</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.001795489891212804</v>
+        <v>0.0001485148721209221</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.002648008017798349</v>
+        <v>0.001105597018320249</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.00100827499296392</v>
+        <v>0.0007145521587080561</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.001434293726106709</v>
+        <v>0.001515966691397263</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.001706898391960004</v>
+        <v>0.0003897639439307693</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0021819232516265</v>
+        <v>0.001113673053136447</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.000669241525645619</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.001163235238383258</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0008189922729503124</v>
+        <v>0.00192771002194531</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0003557258941439807</v>
+        <v>0.001714193037183107</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0005338958275672582</v>
+        <v>0.00257823239351562</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001741653490483075</v>
+        <v>0.001381184326616107</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0001725593825517382</v>
+        <v>0.00116065673656987</v>
       </c>
       <c r="G18" t="n">
-        <v>3.640618836937009e-05</v>
+        <v>0.0015794791170509</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0002445006099946157</v>
+        <v>0.001025081438133275</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0003768135811888518</v>
+        <v>0.001602523624396663</v>
       </c>
       <c r="J18" t="n">
-        <v>0.002042949739237347</v>
+        <v>0.001812581555911887</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0009609441006345953</v>
+        <v>0.001783541595452797</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0001825771650526635</v>
+        <v>0.0003980647080438026</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0009661718559023261</v>
+        <v>0.001991225820532009</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0003511518014231094</v>
+        <v>0.002373404096783979</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0009853846655032564</v>
+        <v>0.0009289847001239207</v>
       </c>
       <c r="P18" t="n">
-        <v>0.001905890187433378</v>
+        <v>0.0009731681211837644</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.001892489048909762</v>
+        <v>0.000598321697506981</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0002178845118927314</v>
+        <v>0.0004135533343666016</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0004760680023887044</v>
+        <v>0.0017467007785229</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0003211833548594775</v>
+        <v>0.001449509570057764</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0002818951437297743</v>
+        <v>0.001026888690973193</v>
       </c>
       <c r="W18" t="n">
-        <v>0.001255224049919188</v>
+        <v>0.001204759640561235</v>
       </c>
       <c r="X18" t="n">
-        <v>0.002051527353120736</v>
+        <v>0.001947584029580321</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.000591850549859012</v>
+        <v>0.002415922460150093</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0001902558304958177</v>
+        <v>0.0005877213335341394</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.001149540710228954</v>
+        <v>0.002414329131869152</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0001175401232264388</v>
+        <v>0.001554652676585857</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0003051050068708597</v>
+        <v>0.0005332613469792829</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0001947744724324563</v>
+        <v>0.001925365219479487</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0002808168742696719</v>
+        <v>0.001734352384474728</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.001232229899254341</v>
+        <v>0.002597178301497543</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.000689823472490883</v>
+        <v>0.001057863291697956</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.0008439983038458658</v>
+        <v>0.001650913289953634</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.001700850473623365</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.002236022983505573</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0008887133956466591</v>
+        <v>0.001895939377903669</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0002410175133161878</v>
+        <v>0.001852020160775047</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0005510999105076578</v>
+        <v>0.002181776746351369</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001568879020927439</v>
+        <v>0.00114987656579224</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0001245285118110584</v>
+        <v>0.001320009058069339</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000181711983251215</v>
+        <v>0.001607883038063238</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0003014856284530918</v>
+        <v>0.001147679963970996</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0007433157877822931</v>
+        <v>0.00147100023656706</v>
       </c>
       <c r="J19" t="n">
-        <v>0.001682187356177555</v>
+        <v>0.001680716548413017</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001379380819484409</v>
+        <v>0.001612373706804183</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0003700053498817857</v>
+        <v>0.0002666862601894223</v>
       </c>
       <c r="M19" t="n">
-        <v>0.001021639259119062</v>
+        <v>0.001733775924531592</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0003935304423977201</v>
+        <v>0.002270122544694154</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0009427400927546259</v>
+        <v>0.0005718779547835796</v>
       </c>
       <c r="P19" t="n">
-        <v>0.001575541937995674</v>
+        <v>0.0009669520684153514</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.001502093288561322</v>
+        <v>0.0003967740579882089</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0002178845118927314</v>
+        <v>0.0004135533343666016</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0004841487382353861</v>
+        <v>0.001740877173151876</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0004768025552687897</v>
+        <v>0.001386688685983714</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0006181604536354575</v>
+        <v>0.0007596586039640187</v>
       </c>
       <c r="W19" t="n">
-        <v>0.0009066763668806227</v>
+        <v>0.0009701928582653012</v>
       </c>
       <c r="X19" t="n">
-        <v>0.001555558890431862</v>
+        <v>0.001767120350659794</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.0005345841563570949</v>
+        <v>0.002422124615442573</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.0004649055073055646</v>
+        <v>0.0009300528914322347</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.00110610684660022</v>
+        <v>0.001847692412262673</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.0002236092874516664</v>
+        <v>0.001351260477555547</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.0006601805764075981</v>
+        <v>0.000631957521041719</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.0004228229636707091</v>
+        <v>0.001816056188825765</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.0003672996141255241</v>
+        <v>0.001654516431957931</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.000760419680559822</v>
+        <v>0.00243948024487533</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.001120018882689968</v>
+        <v>0.0009265925475987518</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.001043998539675221</v>
+        <v>0.001325666103121455</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.001572922420404304</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.002006356522355432</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0007050846297166995</v>
+        <v>0.0007513823518797356</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0006583414051797176</v>
+        <v>0.0003240206069202329</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0008475453567342726</v>
+        <v>0.000487818100482459</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001092728743153681</v>
+        <v>0.001597857843204874</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0003414934695383849</v>
+        <v>0.0001578723007141525</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003746841703850956</v>
+        <v>3.343369806041893e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0002239784832647796</v>
+        <v>0.0002254224393480486</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0004315520136920724</v>
+        <v>8.30349071068523e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.001070533652689224</v>
+        <v>0.0003460825340976554</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0006960949910276221</v>
+        <v>0.0002911677171059705</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0007720724372047881</v>
+        <v>0.001883453115160795</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0002055373749003327</v>
+        <v>0.0008870590821738612</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0001297300971004234</v>
+        <v>0.0001691825019037364</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0002357750824579874</v>
+        <v>0.0008886757856863931</v>
       </c>
       <c r="P20" t="n">
-        <v>0.001129207530400029</v>
+        <v>0.0003245497487817344</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.000834055744066191</v>
+        <v>0.0009120163896364781</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0004760680023887044</v>
+        <v>0.0017467007785229</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0004841487382353861</v>
+        <v>0.001740877173151876</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>7.866882937585066e-05</v>
+        <v>0.000198745103168068</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0004074072183933285</v>
+        <v>0.000436881259361202</v>
       </c>
       <c r="W20" t="n">
-        <v>0.001399905064618536</v>
+        <v>0.0002943391357602362</v>
       </c>
       <c r="X20" t="n">
-        <v>0.001185637885817431</v>
+        <v>0.0002585301647762406</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.0008188089514650605</v>
+        <v>0.001150717100633115</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.0002586273759538183</v>
+        <v>0.001885357824711928</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.0003522772881042944</v>
+        <v>0.0005468565778099329</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.0005797957770896239</v>
+        <v>0.0001745434729773631</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.0003616383434739818</v>
+        <v>0.00105581312486538</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0009004704493784339</v>
+        <v>0.0001087483727515296</v>
       </c>
       <c r="AE20" t="n">
-        <v>8.017266472271946e-05</v>
+        <v>0.0002777797951844097</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0009668270017554796</v>
+        <v>0.0001780045827498216</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.000531338014522453</v>
+        <v>0.0002578866533057099</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.0007650475914214046</v>
+        <v>0.001127836269771906</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.0006369286450218216</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.000772616589771986</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0005760128114861237</v>
+        <v>0.0008167300906715516</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0006305282595228209</v>
+        <v>0.0002189391137765073</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0007014179274033943</v>
+        <v>0.0005042383120965963</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001212022234702346</v>
+        <v>0.001437405552603658</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0003174680774846106</v>
+        <v>0.00011489465301223</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0002566572101739334</v>
+        <v>0.0001661572102916005</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0002234473306927694</v>
+        <v>0.0002787992941303312</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0002139899401579091</v>
+        <v>8.413113393437093e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.001313833219614965</v>
+        <v>0.0006830375806820331</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0004806290282039246</v>
+        <v>0.0006041362066019937</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0005419190584215884</v>
+        <v>0.001553513234853845</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0002787667014334193</v>
+        <v>0.001273442828602049</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0001417570212613574</v>
+        <v>0.0003414984401896217</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0003892960266013671</v>
+        <v>0.0009446330973876842</v>
       </c>
       <c r="P21" t="n">
-        <v>0.001314962495435293</v>
+        <v>0.000362852735203119</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.00105625758944865</v>
+        <v>0.0008728871122113558</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0003211833548594775</v>
+        <v>0.001449509570057764</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0004768025552687897</v>
+        <v>0.001386688685983714</v>
       </c>
       <c r="T21" t="n">
-        <v>7.866882937585066e-05</v>
+        <v>0.000198745103168068</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0002060502083676186</v>
+        <v>0.0004451548515519627</v>
       </c>
       <c r="W21" t="n">
-        <v>0.001421680946326178</v>
+        <v>0.0004375361239546728</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00134141905624434</v>
+        <v>0.0005667727091871149</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.0006717202795505287</v>
+        <v>0.0008306489483668943</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.44576719029638e-05</v>
+        <v>0.001433259991300737</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.0005051338738145187</v>
+        <v>0.0004911258685744746</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.0003935193500273969</v>
+        <v>0.0004274993516957486</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.0001716906215021071</v>
+        <v>0.00101801870652913</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.0006163539704420977</v>
+        <v>0.0002028614911396219</v>
       </c>
       <c r="AE21" t="n">
-        <v>5.287451796071046e-05</v>
+        <v>0.0006025172205526756</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0009235119696182501</v>
+        <v>0.0003869048263740639</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.0002997050154999593</v>
+        <v>0.0003377781153919158</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.000668729762417948</v>
+        <v>0.0006954003823031631</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.001032533151247234</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.0009569270938619015</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0003793657246042414</v>
+        <v>0.0006526162870328111</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0006901420299640717</v>
+        <v>0.0006037106933193898</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0004163623335423063</v>
+        <v>0.0007818401563334951</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001715735845593226</v>
+        <v>0.0009992155358962711</v>
       </c>
       <c r="F22" t="n">
-        <v>0.000455073023747102</v>
+        <v>0.0003132172663195925</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002618473708514384</v>
+        <v>0.0003436155027757735</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0004864994635254567</v>
+        <v>0.000204720468939069</v>
       </c>
       <c r="I22" t="n">
-        <v>4.395259697987325e-05</v>
+        <v>0.0003545424126014538</v>
       </c>
       <c r="J22" t="n">
-        <v>0.002151444118866521</v>
+        <v>0.0003994586326522873</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0002956962265744468</v>
+        <v>0.0003419542614266625</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0002693902948423307</v>
+        <v>0.0009790949008548497</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0006779095717961542</v>
+        <v>0.0006456298934670515</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0004041447949919583</v>
+        <v>0.0007160288281777605</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0009078877578437231</v>
+        <v>0.0001891023600577335</v>
       </c>
       <c r="P22" t="n">
-        <v>0.002125240561508393</v>
+        <v>0.0001192418204722788</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.001919130442407346</v>
+        <v>0.0002170498380736429</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0002818951437297743</v>
+        <v>0.001026888690973193</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0006181604536354575</v>
+        <v>0.0007596586039640187</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0004074072183933285</v>
+        <v>0.000436881259361202</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0002060502083676186</v>
+        <v>0.0004451548515519627</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.001467078665375856</v>
+        <v>7.178923836729178e-05</v>
       </c>
       <c r="X22" t="n">
-        <v>0.001903458628900406</v>
+        <v>0.0003776577751629072</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.0005199781819492287</v>
+        <v>0.001290531358624765</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.0001459835199761735</v>
+        <v>0.001091611668014981</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.001030779192052851</v>
+        <v>0.0007596513420059882</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.0002806280124654841</v>
+        <v>0.0002380606419581928</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.829454048136635e-05</v>
+        <v>0.0003245751212962588</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.000285455552526014</v>
+        <v>0.0005301597155648151</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.0002982453128591398</v>
+        <v>0.0003346513410418411</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.001160398835899607</v>
+        <v>0.000831179018247038</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.0002380225440192279</v>
+        <v>7.242560545577435e-05</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.0004965109131379225</v>
+        <v>0.000889288819428296</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.0004914730428636725</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.0007048794204418847</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.001285523830074373</v>
+        <v>0.0005304475332657358</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0003756265918056387</v>
+        <v>0.0005779844789275251</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0007311358003321603</v>
+        <v>0.0006436570124060748</v>
       </c>
       <c r="E23" t="n">
-        <v>0.002166086743185375</v>
+        <v>0.001111636645602888</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001002799183320044</v>
+        <v>0.0002912171781505407</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001222307910914956</v>
+        <v>0.0002349793762658426</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00133330946446869</v>
+        <v>0.0002037748402321331</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001584249512156351</v>
+        <v>0.0002626741091581477</v>
       </c>
       <c r="J23" t="n">
-        <v>0.002771334381978324</v>
+        <v>0.0001979728921762366</v>
       </c>
       <c r="K23" t="n">
-        <v>0.002085126470484242</v>
+        <v>0.0001390801464763738</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001269103831162302</v>
+        <v>0.001210844948078662</v>
       </c>
       <c r="M23" t="n">
-        <v>0.001881022946944572</v>
+        <v>0.0004457755508827178</v>
       </c>
       <c r="N23" t="n">
-        <v>0.001270951377707928</v>
+        <v>0.0005012232283111047</v>
       </c>
       <c r="O23" t="n">
-        <v>0.001964024177424147</v>
+        <v>0.0002566338968353837</v>
       </c>
       <c r="P23" t="n">
-        <v>0.002623478221648843</v>
+        <v>0.0001302319231303741</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.002625988961381088</v>
+        <v>0.0003611400526751314</v>
       </c>
       <c r="R23" t="n">
-        <v>0.001255224049919188</v>
+        <v>0.001204759640561235</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0009066763668806227</v>
+        <v>0.0009701928582653012</v>
       </c>
       <c r="T23" t="n">
-        <v>0.001399905064618536</v>
+        <v>0.0002943391357602362</v>
       </c>
       <c r="U23" t="n">
-        <v>0.001421680946326178</v>
+        <v>0.0004375361239546728</v>
       </c>
       <c r="V23" t="n">
-        <v>0.001467078665375856</v>
+        <v>7.178923836729178e-05</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.002057577756125108</v>
+        <v>0.0001906176026669296</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.001343369020683771</v>
+        <v>0.001310791617498412</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.001455291783288442</v>
+        <v>0.001237098218121917</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.001903779306695715</v>
+        <v>0.0006188887264442607</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.001256667012724303</v>
+        <v>6.874769814677878e-05</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.001526816511504865</v>
+        <v>0.0004659727801747239</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001217387696164399</v>
+        <v>0.0003594736105367158</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.001357360702014142</v>
+        <v>0.0001585310488623872</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.001343543575621501</v>
+        <v>0.000567062246836342</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.00191219687360977</v>
+        <v>4.796800004579012e-05</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.001309857946305093</v>
+        <v>0.0008470449497186637</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.0002771301170983599</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.0006126783731913309</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.001242476340006791</v>
+        <v>0.0003493494258047794</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001726758319571866</v>
+        <v>0.0006324258913863967</v>
       </c>
       <c r="D24" t="n">
-        <v>0.002204984849524605</v>
+        <v>0.0003803148291132192</v>
       </c>
       <c r="E24" t="n">
-        <v>0.001737144491899774</v>
+        <v>0.001576421819715787</v>
       </c>
       <c r="F24" t="n">
-        <v>0.001265633645241133</v>
+        <v>0.0004182263867419105</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001847527357016201</v>
+        <v>0.0002385415076228028</v>
       </c>
       <c r="H24" t="n">
-        <v>0.001273000945488025</v>
+        <v>0.0004471439480205934</v>
       </c>
       <c r="I24" t="n">
-        <v>0.001753817768437563</v>
+        <v>0.0003209179336690769</v>
       </c>
       <c r="J24" t="n">
-        <v>0.001359737251827888</v>
+        <v>4.075639777228379e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.001654935607047108</v>
+        <v>2.774242433243853e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00248304301091952</v>
+        <v>0.001984402940698347</v>
       </c>
       <c r="M24" t="n">
-        <v>0.001005104152889755</v>
+        <v>0.0002736885649748583</v>
       </c>
       <c r="N24" t="n">
-        <v>0.001073571061846904</v>
+        <v>0.0002485383334990317</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0008709530946671485</v>
+        <v>0.0006234331826337323</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0006384112596619089</v>
+        <v>0.0003752493570915656</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.001002240573863264</v>
+        <v>0.0008426761466731178</v>
       </c>
       <c r="R24" t="n">
-        <v>0.002051527353120736</v>
+        <v>0.001947584029580321</v>
       </c>
       <c r="S24" t="n">
-        <v>0.001555558890431862</v>
+        <v>0.001767120350659794</v>
       </c>
       <c r="T24" t="n">
-        <v>0.001185637885817431</v>
+        <v>0.0002585301647762406</v>
       </c>
       <c r="U24" t="n">
-        <v>0.00134141905624434</v>
+        <v>0.0005667727091871149</v>
       </c>
       <c r="V24" t="n">
-        <v>0.001903458628900406</v>
+        <v>0.0003776577751629072</v>
       </c>
       <c r="W24" t="n">
-        <v>0.002057577756125108</v>
+        <v>0.0001906176026669296</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.001979867901140981</v>
+        <v>0.001348498415907668</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.001728688856556535</v>
+        <v>0.001752019041529331</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.000577820195475223</v>
+        <v>0.0004779887442165121</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.002168975435109582</v>
+        <v>0.0001332353086166499</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.001751787893702881</v>
+        <v>0.0009507087081194789</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.002546815570274467</v>
+        <v>0.0002568454945516968</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.0013847498297744</v>
+        <v>3.563302423673564e-05</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0008328671596897077</v>
+        <v>0.0002617996511956084</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.00153378580303331</v>
+        <v>0.0002741675115961583</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.002190915272420471</v>
+        <v>0.001062905327738453</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.000220424943473933</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.0004574229824304279</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0006717050346133899</v>
+        <v>0.001179816452803758</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0008236302145363631</v>
+        <v>0.0003474782585731413</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0002443025485144512</v>
+        <v>0.000670622510061144</v>
       </c>
       <c r="E25" t="n">
-        <v>0.002009330438616594</v>
+        <v>0.001985685210586573</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0006633132084911676</v>
+        <v>0.0009201272834805371</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000600682608072051</v>
+        <v>0.001123201239531696</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0008579746721776212</v>
+        <v>0.001226397297857511</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0005933479887679188</v>
+        <v>0.0009870790919205808</v>
       </c>
       <c r="J25" t="n">
-        <v>0.002644161984750589</v>
+        <v>0.001457688761406919</v>
       </c>
       <c r="K25" t="n">
-        <v>0.000819951659766891</v>
+        <v>0.001365694734191177</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0005167023291746335</v>
+        <v>0.002551935220806439</v>
       </c>
       <c r="M25" t="n">
-        <v>0.001131428988374953</v>
+        <v>0.001923519465921098</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0007715306325478924</v>
+        <v>0.001169889946327615</v>
       </c>
       <c r="O25" t="n">
-        <v>0.001226816991512277</v>
+        <v>0.001738751139820351</v>
       </c>
       <c r="P25" t="n">
-        <v>0.002627488709339958</v>
+        <v>0.001169921300370555</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.001998407576051388</v>
+        <v>0.001810731174035727</v>
       </c>
       <c r="R25" t="n">
-        <v>0.000591850549859012</v>
+        <v>0.002415922460150093</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0005345841563570949</v>
+        <v>0.002422124615442573</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0008188089514650605</v>
+        <v>0.001150717100633115</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0006717202795505287</v>
+        <v>0.0008306489483668943</v>
       </c>
       <c r="V25" t="n">
-        <v>0.0005199781819492287</v>
+        <v>0.001290531358624765</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001343369020683771</v>
+        <v>0.001310791617498412</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001979867901140981</v>
+        <v>0.001348498415907668</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.0006279146099057159</v>
+        <v>0.00189628108075076</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.001565410431887502</v>
+        <v>0.00123421637823522</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.0004962234266894608</v>
+        <v>0.001338664555545017</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.0006361569453716219</v>
+        <v>0.001754558237345472</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.0003942980183375275</v>
+        <v>0.001152425517519135</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.0008444886614967069</v>
+        <v>0.001402399548400035</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0005935005124987591</v>
+        <v>0.001118758310430753</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.0008180036648180892</v>
+        <v>0.001250975062767999</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.0009842554951769349</v>
+        <v>0.001233485691712764</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.001763666079118676</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.001205481472758834</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0006704553353592415</v>
+        <v>0.001142666634345456</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0006349636716968976</v>
+        <v>0.00158854422249802</v>
       </c>
       <c r="D26" t="n">
-        <v>0.000628000880164708</v>
+        <v>0.002032329871801095</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001555082757405248</v>
+        <v>0.001599456862301244</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0003495230634467284</v>
+        <v>0.001163475688143723</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0001894688456317687</v>
+        <v>0.001700395903832415</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0003079788323795797</v>
+        <v>0.001171044663320596</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0002089090324581867</v>
+        <v>0.001655830099713792</v>
       </c>
       <c r="J26" t="n">
-        <v>0.001736381397792583</v>
+        <v>0.001618374181006107</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0005151443594724576</v>
+        <v>0.00158854639330044</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0003960969089634869</v>
+        <v>0.001253215704542814</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0005033470694677621</v>
+        <v>0.001527867656962752</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0003069984941326503</v>
+        <v>0.002294766277059003</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0007078920559901747</v>
+        <v>0.0009302886180025908</v>
       </c>
       <c r="P26" t="n">
-        <v>0.001696145906873619</v>
+        <v>0.0009872349880386405</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.001468260481752453</v>
+        <v>0.0008004786135067206</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0001902558304958177</v>
+        <v>0.0005877213335341394</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0004649055073055646</v>
+        <v>0.0009300528914322347</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0002586273759538183</v>
+        <v>0.001885357824711928</v>
       </c>
       <c r="U26" t="n">
-        <v>7.44576719029638e-05</v>
+        <v>0.001433259991300737</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0001459835199761735</v>
+        <v>0.001091611668014981</v>
       </c>
       <c r="W26" t="n">
-        <v>0.001455291783288442</v>
+        <v>0.001237098218121917</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001728688856556535</v>
+        <v>0.001752019041529331</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.0006279146099057159</v>
+        <v>0.00189628108075076</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.0008697501420532635</v>
+        <v>0.001824230111983142</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.0002620625642974204</v>
+        <v>0.001591225702698504</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.0001722114947355752</v>
+        <v>0.0005310983701284043</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.0003744080914572253</v>
+        <v>0.001989140363557597</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.0001274572016834331</v>
+        <v>0.001613750404435008</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.001043623529131143</v>
+        <v>0.002345132087377298</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.000353563185326596</v>
+        <v>0.00127565979209584</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.0008091184120756849</v>
+        <v>0.0007673140819156701</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.001416156627282812</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.002017402327143837</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0008985992099697465</v>
+        <v>0.0006170372965547407</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001158520461449765</v>
+        <v>0.0007585036410811811</v>
       </c>
       <c r="D27" t="n">
-        <v>0.001651639777173672</v>
+        <v>0.0002255672424890834</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001114406322397396</v>
+        <v>0.001847570421228349</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0007002475755859105</v>
+        <v>0.0006116162362548135</v>
       </c>
       <c r="G27" t="n">
-        <v>0.001010933927398733</v>
+        <v>0.0005518773139429644</v>
       </c>
       <c r="H27" t="n">
-        <v>0.000498931608183618</v>
+        <v>0.0007949968382678804</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0008628443351934343</v>
+        <v>0.0004422534211602636</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0009156049330775972</v>
+        <v>0.0005470950073030169</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0009767973534421314</v>
+        <v>0.0004844895319552453</v>
       </c>
       <c r="L27" t="n">
-        <v>0.001636244959534286</v>
+        <v>0.00243760390415735</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0003215885878310229</v>
+        <v>0.000758091903814427</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0002863494369617702</v>
+        <v>0.00047486127750388</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0001605406551612901</v>
+        <v>0.001043562066994184</v>
       </c>
       <c r="P27" t="n">
-        <v>0.000579821799164318</v>
+        <v>0.0007135202835157633</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.000684883988367931</v>
+        <v>0.001137226250333115</v>
       </c>
       <c r="R27" t="n">
-        <v>0.001149540710228954</v>
+        <v>0.002414329131869152</v>
       </c>
       <c r="S27" t="n">
-        <v>0.00110610684660022</v>
+        <v>0.001847692412262673</v>
       </c>
       <c r="T27" t="n">
-        <v>0.0003522772881042944</v>
+        <v>0.0005468565778099329</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0005051338738145187</v>
+        <v>0.0004911258685744746</v>
       </c>
       <c r="V27" t="n">
-        <v>0.001030779192052851</v>
+        <v>0.0007596513420059882</v>
       </c>
       <c r="W27" t="n">
-        <v>0.001903779306695715</v>
+        <v>0.0006188887264442607</v>
       </c>
       <c r="X27" t="n">
-        <v>0.000577820195475223</v>
+        <v>0.0004779887442165121</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.001565410431887502</v>
+        <v>0.00123421637823522</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.0008697501420532635</v>
+        <v>0.001824230111983142</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.001440227676700012</v>
+        <v>0.0005786248013228273</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.0008137040487573229</v>
+        <v>0.001442665660218116</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.001828225059816454</v>
+        <v>0.0004557586360716323</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.0005455359268416839</v>
+        <v>0.0005843971664293949</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.001236399438837724</v>
+        <v>0.000365686768165091</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.0006964282701781972</v>
+        <v>0.0007761508655819797</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.00115350052858182</v>
+        <v>0.000546095881208634</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.0007560918321428617</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.0009051884965855358</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.00085192071921391</v>
+        <v>0.0006143655114641051</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0004412952736959169</v>
+        <v>0.000580942470890185</v>
       </c>
       <c r="D28" t="n">
-        <v>0.000463096989072066</v>
+        <v>0.0005744231637729196</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001722768245534182</v>
+        <v>0.00143271442785617</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0002918294706358513</v>
+        <v>0.0003208146939314943</v>
       </c>
       <c r="G28" t="n">
-        <v>8.58077909639838e-05</v>
+        <v>0.0001747942434498551</v>
       </c>
       <c r="H28" t="n">
-        <v>0.000426092386869266</v>
+        <v>0.0002824373298970249</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0004231762476388277</v>
+        <v>0.0002084422843551238</v>
       </c>
       <c r="J28" t="n">
-        <v>0.002046437451690213</v>
+        <v>0.0001913411960153858</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001018486140962187</v>
+        <v>0.0001154691307259772</v>
       </c>
       <c r="L28" t="n">
-        <v>8.733048680003559e-05</v>
+        <v>0.001604375138620095</v>
       </c>
       <c r="M28" t="n">
-        <v>0.001159856778267721</v>
+        <v>0.0004746655302521723</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0005292452486440013</v>
+        <v>0.0003660255095482305</v>
       </c>
       <c r="O28" t="n">
-        <v>0.001199446411302169</v>
+        <v>0.0004614748764536193</v>
       </c>
       <c r="P28" t="n">
-        <v>0.002106672589418343</v>
+        <v>0.0002834291781065498</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.001978411582784225</v>
+        <v>0.0006551269598988984</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0001175401232264388</v>
+        <v>0.001554652676585857</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0002236092874516664</v>
+        <v>0.001351260477555547</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0005797957770896239</v>
+        <v>0.0001745434729773631</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0003935193500273969</v>
+        <v>0.0004274993516957486</v>
       </c>
       <c r="V28" t="n">
-        <v>0.0002806280124654841</v>
+        <v>0.0002380606419581928</v>
       </c>
       <c r="W28" t="n">
-        <v>0.001256667012724303</v>
+        <v>6.874769814677878e-05</v>
       </c>
       <c r="X28" t="n">
-        <v>0.002168975435109582</v>
+        <v>0.0001332353086166499</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.0004962234266894608</v>
+        <v>0.001338664555545017</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.0002620625642974204</v>
+        <v>0.001591225702698504</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.001440227676700012</v>
+        <v>0.0005786248013228273</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.0003524111529179582</v>
+        <v>0.0008006437858872384</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.0001575366842370619</v>
+        <v>0.0002415088978531364</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.0003305239711677276</v>
+        <v>0.0001569579324270206</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.001123582611300192</v>
+        <v>0.0003435962154772695</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.0008370211974602084</v>
+        <v>0.0001168625155553124</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.0008374055859909681</v>
+        <v>0.0009558032556002086</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.0003250203339682896</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.0007415101862182184</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0003568289358862321</v>
+        <v>0.0008260085888793886</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0006726489226879656</v>
+        <v>0.001065139016481779</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0005465416871457381</v>
+        <v>0.0015189479695366</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001562866630468713</v>
+        <v>0.00102360243704858</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0004132250741621741</v>
+        <v>0.0006436485933496159</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0002621131614792093</v>
+        <v>0.0009289500676977891</v>
       </c>
       <c r="H29" t="n">
-        <v>0.000387204691291828</v>
+        <v>0.0004586960877391048</v>
       </c>
       <c r="I29" t="n">
-        <v>1.436828701998398e-05</v>
+        <v>0.0009968543668672106</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00198421236456719</v>
+        <v>0.0007963779503813845</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0003022135642022283</v>
+        <v>0.0008024508147327597</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0003240969929131481</v>
+        <v>0.0008450477278618562</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0006355516513227594</v>
+        <v>0.0009028975291566211</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0002781741912163569</v>
+        <v>0.00151326028929544</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0007681800900361795</v>
+        <v>0.0003026639935682863</v>
       </c>
       <c r="P29" t="n">
-        <v>0.001891856234045607</v>
+        <v>0.000262672720055964</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.001795489891212804</v>
+        <v>0.0001485148721209221</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0003051050068708597</v>
+        <v>0.0005332613469792829</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0006601805764075981</v>
+        <v>0.000631957521041719</v>
       </c>
       <c r="T29" t="n">
-        <v>0.0003616383434739818</v>
+        <v>0.00105581312486538</v>
       </c>
       <c r="U29" t="n">
-        <v>0.0001716906215021071</v>
+        <v>0.00101801870652913</v>
       </c>
       <c r="V29" t="n">
-        <v>3.829454048136635e-05</v>
+        <v>0.0003245751212962588</v>
       </c>
       <c r="W29" t="n">
-        <v>0.001526816511504865</v>
+        <v>0.0004659727801747239</v>
       </c>
       <c r="X29" t="n">
-        <v>0.001751787893702881</v>
+        <v>0.0009507087081194789</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.0006361569453716219</v>
+        <v>0.001754558237345472</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.0001722114947355752</v>
+        <v>0.0005310983701284043</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.0008137040487573229</v>
+        <v>0.001442665660218116</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.0003524111529179582</v>
+        <v>0.0008006437858872384</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.000409442881483092</v>
+        <v>0.001319499265434813</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.000268499513514591</v>
+        <v>0.0007511699262645314</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.001219837825088116</v>
+        <v>0.001682521274262578</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.0001487706842170794</v>
+        <v>0.0005048141861859586</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.0004118650168487059</v>
+        <v>0.001134531139962528</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.0006429759003685994</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.001060476425944397</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0007105978158151942</v>
+        <v>0.0007807645613429068</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0005277097173825658</v>
+        <v>0.0004015776054006642</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0002714398906704753</v>
+        <v>0.0004239593281928185</v>
       </c>
       <c r="E30" t="n">
-        <v>0.002256965051599172</v>
+        <v>0.001578350918414937</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0004842410899607567</v>
+        <v>0.0002661216037368953</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0002614458646951273</v>
+        <v>7.736677851482131e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0007198097580423382</v>
+        <v>0.0003887959328761918</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0004208804738280851</v>
+        <v>0.0001100786368624052</v>
       </c>
       <c r="J30" t="n">
-        <v>0.002908325501853875</v>
+        <v>0.0003879237067488796</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0009420012257357977</v>
+        <v>0.0003134854059379621</v>
       </c>
       <c r="L30" t="n">
-        <v>9.254133801157968e-05</v>
+        <v>0.001882779321381557</v>
       </c>
       <c r="M30" t="n">
-        <v>0.001408366759400697</v>
+        <v>0.0009386981595419807</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0007753213606968911</v>
+        <v>8.184360849392175e-05</v>
       </c>
       <c r="O30" t="n">
-        <v>0.001637738924700102</v>
+        <v>0.00106316065206885</v>
       </c>
       <c r="P30" t="n">
-        <v>0.002832744327091317</v>
+        <v>0.0004855538673447159</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.002648008017798349</v>
+        <v>0.001105597018320249</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0001947744724324563</v>
+        <v>0.001925365219479487</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0004228229636707091</v>
+        <v>0.001816056188825765</v>
       </c>
       <c r="T30" t="n">
-        <v>0.0009004704493784339</v>
+        <v>0.0001087483727515296</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0006163539704420977</v>
+        <v>0.0002028614911396219</v>
       </c>
       <c r="V30" t="n">
-        <v>0.000285455552526014</v>
+        <v>0.0005301597155648151</v>
       </c>
       <c r="W30" t="n">
-        <v>0.001217387696164399</v>
+        <v>0.0003594736105367158</v>
       </c>
       <c r="X30" t="n">
-        <v>0.002546815570274467</v>
+        <v>0.0002568454945516968</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.0003942980183375275</v>
+        <v>0.001152425517519135</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.0003744080914572253</v>
+        <v>0.001989140363557597</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.001828225059816454</v>
+        <v>0.0004557586360716323</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.0001575366842370619</v>
+        <v>0.0002415088978531364</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.000409442881483092</v>
+        <v>0.001319499265434813</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.000661934685430906</v>
+        <v>0.000319973594644362</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.00119723373062331</v>
+        <v>0.0001448113823295361</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.0008057056594190064</v>
+        <v>0.0003009420825999833</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.0008403924289345988</v>
+        <v>0.001025251924335476</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.0007701467697829614</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.0007668763005159401</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0007563564359911485</v>
+        <v>0.000329360095738865</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0005443910560980392</v>
+        <v>0.0006130862589778318</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0008111648882581048</v>
+        <v>0.0004994610340200813</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001167786952271799</v>
+        <v>0.001439243799055461</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0002503286509666548</v>
+        <v>0.0003771330630226638</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0001992397482210417</v>
+        <v>0.0002358237791211742</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0001801426202293689</v>
+        <v>0.0003524924095475407</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0003501762099204773</v>
+        <v>0.000351065904478879</v>
       </c>
       <c r="J31" t="n">
-        <v>0.001099690467847303</v>
+        <v>1.357558324999227e-05</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0007448324758642853</v>
+        <v>1.980039061834554e-05</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0005282140872573138</v>
+        <v>0.001832932530149019</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0003813039578177212</v>
+        <v>0.0002817492987649042</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0001597753122251881</v>
+        <v>0.0002974829067311284</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0004198899322241442</v>
+        <v>0.0005875446479687256</v>
       </c>
       <c r="P31" t="n">
-        <v>0.001152953884313398</v>
+        <v>0.0002570700728000484</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.00100827499296392</v>
+        <v>0.0007145521587080561</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0002808168742696719</v>
+        <v>0.001734352384474728</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0003672996141255241</v>
+        <v>0.001654516431957931</v>
       </c>
       <c r="T31" t="n">
-        <v>8.017266472271946e-05</v>
+        <v>0.0002777797951844097</v>
       </c>
       <c r="U31" t="n">
-        <v>5.287451796071046e-05</v>
+        <v>0.0006025172205526756</v>
       </c>
       <c r="V31" t="n">
-        <v>0.0002982453128591398</v>
+        <v>0.0003346513410418411</v>
       </c>
       <c r="W31" t="n">
-        <v>0.001357360702014142</v>
+        <v>0.0001585310488623872</v>
       </c>
       <c r="X31" t="n">
-        <v>0.0013847498297744</v>
+        <v>3.563302423673564e-05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.0008444886614967069</v>
+        <v>0.001402399548400035</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.0001274572016834331</v>
+        <v>0.001613750404435008</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.0005455359268416839</v>
+        <v>0.0005843971664293949</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.0003305239711677276</v>
+        <v>0.0001569579324270206</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.000268499513514591</v>
+        <v>0.0007511699262645314</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.000661934685430906</v>
+        <v>0.000319973594644362</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.001066530675583104</v>
+        <v>0.0003733045966879265</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.0005338171777648148</v>
+        <v>0.0002464044472977945</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.0007610949163154935</v>
+        <v>0.00111830673187282</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.0001388704909862787</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.000379386034194676</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0007968616093256464</v>
+        <v>0.0006556667698393208</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001099873854784032</v>
+        <v>0.000482713742164949</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0009387980959422803</v>
+        <v>0.0002506604538193051</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00192418819958491</v>
+        <v>0.002072917883536743</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0009294636274873341</v>
+        <v>0.0004447822162491587</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00114722149780883</v>
+        <v>0.0002380224136395489</v>
       </c>
       <c r="H32" t="n">
-        <v>0.001065105008963174</v>
+        <v>0.000661694094570018</v>
       </c>
       <c r="I32" t="n">
-        <v>0.001178319022825877</v>
+        <v>0.0002184717153921187</v>
       </c>
       <c r="J32" t="n">
-        <v>0.002069556331216138</v>
+        <v>0.0003868418662462296</v>
       </c>
       <c r="K32" t="n">
-        <v>0.00130429696828827</v>
+        <v>0.0003383802329893899</v>
       </c>
       <c r="L32" t="n">
-        <v>0.001298151159541111</v>
+        <v>0.002679778215137817</v>
       </c>
       <c r="M32" t="n">
-        <v>0.001112212321176857</v>
+        <v>0.0008723806560342092</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0009369026776663298</v>
+        <v>8.269582661849213e-05</v>
       </c>
       <c r="O32" t="n">
-        <v>0.001211217256989852</v>
+        <v>0.001298225664156673</v>
       </c>
       <c r="P32" t="n">
-        <v>0.001800708939275026</v>
+        <v>0.0007159141578456929</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.001434293726106709</v>
+        <v>0.001515966691397263</v>
       </c>
       <c r="R32" t="n">
-        <v>0.001232229899254341</v>
+        <v>0.002597178301497543</v>
       </c>
       <c r="S32" t="n">
-        <v>0.000760419680559822</v>
+        <v>0.00243948024487533</v>
       </c>
       <c r="T32" t="n">
-        <v>0.0009668270017554796</v>
+        <v>0.0001780045827498216</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0009235119696182501</v>
+        <v>0.0003869048263740639</v>
       </c>
       <c r="V32" t="n">
-        <v>0.001160398835899607</v>
+        <v>0.000831179018247038</v>
       </c>
       <c r="W32" t="n">
-        <v>0.001343543575621501</v>
+        <v>0.000567062246836342</v>
       </c>
       <c r="X32" t="n">
-        <v>0.0008328671596897077</v>
+        <v>0.0002617996511956084</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.0005935005124987591</v>
+        <v>0.001118758310430753</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.001043623529131143</v>
+        <v>0.002345132087377298</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.001236399438837724</v>
+        <v>0.000365686768165091</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.001123582611300192</v>
+        <v>0.0003435962154772695</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.001219837825088116</v>
+        <v>0.001682521274262578</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.00119723373062331</v>
+        <v>0.0001448113823295361</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.001066530675583104</v>
+        <v>0.0003733045966879265</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.001225336274078719</v>
+        <v>0.0006070190958658825</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.001617932883432193</v>
+        <v>0.001100308706427135</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.0007440144020776206</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.0007721057128936075</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0003622270266783732</v>
+        <v>0.0006960329494242858</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00110236063116846</v>
+        <v>0.0004987539268456534</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0008361026982451372</v>
+        <v>0.0007436574021558543</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001664856750988457</v>
+        <v>0.001075356221479535</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0007376367844341717</v>
+        <v>0.0002300155109826756</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0006679623851152981</v>
+        <v>0.0001824717348529485</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0006370883985794981</v>
+        <v>0.0001641081745500216</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0001022423530875212</v>
+        <v>0.0002233319533999849</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002109692351047512</v>
+        <v>0.0003223407711684459</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0001307230406540463</v>
+        <v>0.0002573467933595503</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0007985210307114768</v>
+        <v>0.001018702756597264</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0005233106718387654</v>
+        <v>0.0006870397710954473</v>
       </c>
       <c r="N33" t="n">
-        <v>0.000414290060890749</v>
+        <v>0.0004895935199840354</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0007199416592024963</v>
+        <v>0.0003513827322599993</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001852270625718384</v>
+        <v>0.0001481198400478676</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.001706898391960004</v>
+        <v>0.0003897639439307693</v>
       </c>
       <c r="R33" t="n">
-        <v>0.000689823472490883</v>
+        <v>0.001057863291697956</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001120018882689968</v>
+        <v>0.0009265925475987518</v>
       </c>
       <c r="T33" t="n">
-        <v>0.000531338014522453</v>
+        <v>0.0002578866533057099</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0002997050154999593</v>
+        <v>0.0003377781153919158</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0002380225440192279</v>
+        <v>7.242560545577435e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>0.00191219687360977</v>
+        <v>4.796800004579012e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>0.00153378580303331</v>
+        <v>0.0002741675115961583</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0008180036648180892</v>
+        <v>0.001250975062767999</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.000353563185326596</v>
+        <v>0.00127565979209584</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0006964282701781972</v>
+        <v>0.0007761508655819797</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0008370211974602084</v>
+        <v>0.0001168625155553124</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.0001487706842170794</v>
+        <v>0.0005048141861859586</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.0008057056594190064</v>
+        <v>0.0003009420825999833</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.0005338171777648148</v>
+        <v>0.0002464044472977945</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.001225336274078719</v>
+        <v>0.0006070190958658825</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.000600249141081601</v>
+        <v>0.0009742437920448769</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.0004918661120683983</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.0007014817969312365</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.0007327539440427072</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.001006208961679693</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0008647056985674345</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.00176641522965629</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.0008517331751441541</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.001049355072041059</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0009771779376524848</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.00086179610112322</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.001085342051296152</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.0009824199886030677</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.001903179696257075</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.001204212545005291</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.001193228641182339</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.001023997836150762</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.0008589785769892768</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.001113673053136447</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.001650913289953634</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.001325666103121455</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.001127836269771906</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.0006954003823031631</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.000889288819428296</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.0008470449497186637</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.001062905327738453</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.001233485691712764</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.0007673140819156701</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.000546095881208634</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.0009558032556002086</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.001134531139962528</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.001025251924335476</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.00111830673187282</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.001100308706427135</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.0009742437920448769</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.001130361074186577</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.001487521813173307</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.0003332940231162733</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001015511830969264</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0007688982114794731</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.001529812442630157</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0006808024429510304</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0006143365160705871</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.0005875707326249558</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.0007133931599123397</v>
+      </c>
+      <c r="J35" t="n">
+        <v>9.479217474500328e-05</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.0001192768454337162</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.001944814843562906</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.0001211958553906719</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.0007378371313146545</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.0004820587851153488</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.0003839532349318538</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.000669241525645619</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.001700850473623365</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.001572922420404304</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.0006369286450218216</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.001032533151247234</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.0004914730428636725</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.0002771301170983599</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.000220424943473933</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.001763666079118676</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.001416156627282812</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.0007560918321428617</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.0003250203339682896</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.0006429759003685994</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.0007701467697829614</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.0001388704909862787</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.0007440144020776206</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.0004918661120683983</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.001130361074186577</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.0005480436263616885</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
           <t>United States of America</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0.0004395683556382205</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.0008212487233807039</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.0005896801730930205</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.001203540233413925</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.0008691377581414224</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0008031273095609697</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0009688868282246409</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.0003989846598532089</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.002097903732869841</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.0008302898942415286</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.0005873371268735817</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.001103597094871415</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.0006283804084501329</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.001256690773665351</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.002436956164627873</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.0021819232516265</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.0008439983038458658</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.001043998539675221</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.0007650475914214046</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.000668729762417948</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.0004965109131379225</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.001309857946305093</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.002190915272420471</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0.0009842554951769349</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0.0008091184120756849</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.00115350052858182</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.0008374055859909681</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.0004118650168487059</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.0008403924289345988</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.0007610949163154935</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0.001617932883432193</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0.000600249141081601</v>
-      </c>
-      <c r="AH34" t="n">
+      <c r="B36" t="n">
+        <v>0.0004026950764687538</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0007543415635248042</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.000540203006459825</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.001105107074934204</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.0007971401356311099</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0007295634316116848</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0008871872360489022</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.0007381343346261206</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.0003660899335937388</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.000431789655251773</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.00193483644979774</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.0007653477736133719</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.0005413141829479201</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.001017213217113181</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.0005777622690089026</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.001163235238383258</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.002236022983505573</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.002006356522355432</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.000772616589771986</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.0009569270938619015</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.0007048794204418847</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.0006126783731913309</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.0004574229824304279</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.001205481472758834</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.002017402327143837</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.0009051884965855358</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.0007415101862182184</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.001060476425944397</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.0007668763005159401</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.000379386034194676</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.0007721057128936075</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.0007014817969312365</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.001487521813173307</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.0005480436263616885</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>0</v>
       </c>
     </row>
